--- a/Project Hotel Booking System.xlsx
+++ b/Project Hotel Booking System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\code_java\HotelBooking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B333D89-CA9C-436A-A402-757912CEC243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7832709D-9EEB-40F7-B882-5826856F4F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
   <si>
     <t>STT</t>
   </si>
@@ -169,9 +169,6 @@
     <t>Làm file TC</t>
   </si>
   <si>
-    <t>Đang thực hiện</t>
-  </si>
-  <si>
     <t>Thực hiện test case</t>
   </si>
   <si>
@@ -182,6 +179,12 @@
   </si>
   <si>
     <t>Tổng quát phần code</t>
+  </si>
+  <si>
+    <t>Trễ hạn</t>
+  </si>
+  <si>
+    <t>Không làm được (Vì file jar không tạo được)</t>
   </si>
 </sst>
 </file>
@@ -893,7 +896,7 @@
         <v>Nhiệm vụ hoàn thành</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1301,7 +1304,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>9</v>
@@ -1343,10 +1346,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>24</v>
@@ -1359,19 +1362,21 @@
       </c>
       <c r="G33" s="2" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Còn 0 ngày</v>
-      </c>
-      <c r="H33" s="3"/>
+        <v>Trễ 0 ngày</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>10</v>
@@ -1384,7 +1389,7 @@
       </c>
       <c r="G34" s="2" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Còn 0 ngày</v>
+        <v>Nhiệm vụ hoàn thành</v>
       </c>
       <c r="H34" s="3"/>
     </row>
